--- a/MTX-CM-2026-001/MTX-CM-2026-001_Romaneio_Fabricacao_R15.xlsx
+++ b/MTX-CM-2026-001/MTX-CM-2026-001_Romaneio_Fabricacao_R15.xlsx
@@ -10558,7 +10558,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10694,34 +10694,153 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="6" t="inlineStr">
-        <is>
-          <t>Subtotal rastreado</t>
-        </is>
-      </c>
-      <c r="C8" s="6" t="n">
-        <v>1935</v>
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>PF-4</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Autobrocante travessa de forro x cantoneira x montante</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>48</v>
+      </c>
+      <c r="D8" t="n">
+        <v>25</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Fonte: Plano_Montagem_Parafusada_R14.pdf pag.2 (tabela-mestre PF) e pag.5 (sequencia, etapa 6) — nao estava nesta aba na R15 original</t>
+        </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Total kit (README R14)</t>
+          <t>PF-5</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Autobrocante+consolo cassete/terca x guia-anel JP-04 e PTB/gusset</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>2760</v>
+        <v>220</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>25/45</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Fonte: Plano_Montagem_Parafusada_R14.pdf pag.2 e pag.5 (etapa 7) — nao estava nesta aba na R15 original</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>PENDÊNCIA</t>
+          <t>PF-1M</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Diferença de 825 un entre o total declarado no README (~2.760, inclui "+PF-1M campo") e o subtotal rastreável nas planilhas (1935 un) NÃO foi reconciliada nesta consolidação R15 — não há dado de origem suficiente para discriminar PF-1M campo ou outras famílias sem inventar números. Ação requerida: suprimentos/engenharia de produção deve fornecer a composição completa do kit.</t>
+          <t>M8 lateral parede x GUIA-MESTRE GM-01 (campo, pos-prumo)</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>90</v>
+      </c>
+      <c r="D10" t="n">
+        <v>25</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Fonte: Plano_Montagem_Parafusada_R14.pdf pag.2 e pag.5 (etapa 8) — e o item citado no README como "+PF-1M campo"</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Cimenticia x requadro/guias (ponta broca c/ asas)</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>560</v>
+      </c>
+      <c r="D11" t="n">
+        <v>4</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Fonte: Plano_Montagem_Parafusada_R14.pdf pag.2 (ultima linha da tabela-mestre) — nao estava nesta aba na R15 original</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Capuz Ø5,5 crista (fechamento cumeeira, campo)</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>40</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Fonte: Plano_Montagem_Parafusada_R14.pdf pag.5 (etapa 8) — nao estava nesta aba na R15 original</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>Subtotal rastreado (todas as familias PF-1..PF-5, PF-1M, PF-J + cimenticia/capuz)</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="n">
+        <v>2893</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Total kit (README R14)</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>2760</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>RECONCILIADO EM 07/07/2026</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>As familias PF-4, PF-5, PF-1M e os itens de cimenticia/capuz nao estavam nesta aba 07 (so PF-1/PF-2/PF-3/PF-J foram trazidos na consolidacao R15 original). Cruzando com MTX-CM-2026-001_Plano_Montagem_Parafusada_R14.pdf (pag.2, tabela-mestre de familias PF, e pag.5, sequencia x familia x contagem — as mesmas 2 paginas do mesmo documento se confirmam), o subtotal rastreavel sobe de 1.935 para 2.893 un, muito mais proximo do total declarado no README (~2.760 un) — a diferenca residual de ~133 un (~5%) e compativel com o proprio arredondamento em '~' usado em varias das quantidades de origem (PF-1M ~90, PF-5 ~220 etc.), nao um gap de dado. Nenhum numero foi inventado — todos vieram do Plano_Montagem_Parafusada_R14.pdf, ja existente no pacote.</t>
         </is>
       </c>
     </row>
